--- a/bills/huixinjiqiren/-5585070216/fb959c2cacc9c000a1cd5487b775e89da035f9898b2fed9930724428cc85cf6d/bill-all.xlsx
+++ b/bills/huixinjiqiren/-5585070216/fb959c2cacc9c000a1cd5487b775e89da035f9898b2fed9930724428cc85cf6d/bill-all.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>09/24 21:20:03</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>36885</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>4668.99</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>SH9982</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>09/24 17:17:34</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>50000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>7.8</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>6410.26</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>50000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6410.26</t>
+          <t>86885</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11079.24</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>6410.26</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>11079.24</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5585070216/fb959c2cacc9c000a1cd5487b775e89da035f9898b2fed9930724428cc85cf6d/bill-all.xlsx
+++ b/bills/huixinjiqiren/-5585070216/fb959c2cacc9c000a1cd5487b775e89da035f9898b2fed9930724428cc85cf6d/bill-all.xlsx
@@ -241,59 +241,86 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>09/24 22:38:21</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>6410</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>SH6669</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>86885</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>11079.24</t>
+          <t>86885</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11079.24</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>6410</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>11079.24</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>4669.24</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5585070216/fb959c2cacc9c000a1cd5487b775e89da035f9898b2fed9930724428cc85cf6d/bill-all.xlsx
+++ b/bills/huixinjiqiren/-5585070216/fb959c2cacc9c000a1cd5487b775e89da035f9898b2fed9930724428cc85cf6d/bill-all.xlsx
@@ -244,83 +244,110 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>09/24 22:41:05</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>4669</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Nikotian01</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>09/24 22:38:21</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>6410</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>SH6669</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>86885</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>11079.24</t>
+          <t>86885</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>6410</t>
+          <t>11079.24</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>11079</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>4669.24</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0.24</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5585070216/fb959c2cacc9c000a1cd5487b775e89da035f9898b2fed9930724428cc85cf6d/bill-all.xlsx
+++ b/bills/huixinjiqiren/-5585070216/fb959c2cacc9c000a1cd5487b775e89da035f9898b2fed9930724428cc85cf6d/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/24 21:20:03</t>
+          <t>09/25 11:47:11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>36885</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4668.99</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,237 +117,279 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>09/24 21:20:03</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>36885</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>4668.99</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>SH9982</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>09/24 17:17:34</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>50000</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>7.8</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>6410.26</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/24 22:41:05</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4669</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>09/24 22:41:05</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>4669</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Nikotian01</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>09/24 22:38:21</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>6410</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>SH6669</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>86885</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>11079.24</t>
+          <t>186885</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>11079</t>
+          <t>23127.44</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>11079</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>0.24</t>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>12048.44</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5585070216/fb959c2cacc9c000a1cd5487b775e89da035f9898b2fed9930724428cc85cf6d/bill-all.xlsx
+++ b/bills/huixinjiqiren/-5585070216/fb959c2cacc9c000a1cd5487b775e89da035f9898b2fed9930724428cc85cf6d/bill-all.xlsx
@@ -75,7 +75,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/25 11:47:11</t>
+          <t>09/29 11:20:18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/24 21:20:03</t>
+          <t>09/25 11:47:11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>36885</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4668.99</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,237 +159,279 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>09/24 21:20:03</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>36885</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>4668.99</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>SH9982</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>09/24 17:17:34</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>50000</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>7.8</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>6410.26</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/24 22:41:05</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4669</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>09/24 22:41:05</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>4669</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Nikotian01</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>09/24 22:38:21</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>6410</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>SH6669</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>186885</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>23127.44</t>
+          <t>286885</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>11079</t>
+          <t>35175.63</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>11079</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>12048.44</t>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>24096.63</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5585070216/fb959c2cacc9c000a1cd5487b775e89da035f9898b2fed9930724428cc85cf6d/bill-all.xlsx
+++ b/bills/huixinjiqiren/-5585070216/fb959c2cacc9c000a1cd5487b775e89da035f9898b2fed9930724428cc85cf6d/bill-all.xlsx
@@ -328,12 +328,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/24 22:41:05</t>
+          <t>09/29 11:20:25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4669</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -343,7 +343,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>SH9982</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -355,83 +355,110 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>09/24 22:41:05</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>4669</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Nikotian01</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>09/24 22:38:21</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>6410</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>SH6669</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>286885</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>35175.63</t>
+          <t>286885</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>11079</t>
+          <t>35175.63</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>11467</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>24096.63</t>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>23708.63</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5585070216/fb959c2cacc9c000a1cd5487b775e89da035f9898b2fed9930724428cc85cf6d/bill-all.xlsx
+++ b/bills/huixinjiqiren/-5585070216/fb959c2cacc9c000a1cd5487b775e89da035f9898b2fed9930724428cc85cf6d/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/29 11:20:18</t>
+          <t>09/30 22:50:49</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>18072.29</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,7 +117,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/25 11:47:11</t>
+          <t>09/29 11:20:18</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/24 21:20:03</t>
+          <t>09/25 11:47:11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>36885</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>4668.99</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,166 +201,181 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>09/24 21:20:03</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>36885</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>4668.99</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>SH9982</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>09/24 17:17:34</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>50000</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>7.8</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>6410.26</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/29 11:20:25</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SH9982</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/24 22:41:05</t>
+          <t>09/29 11:20:25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>4669</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -370,7 +385,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>SH9982</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -382,83 +397,110 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>09/24 22:41:05</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>4669</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Nikotian01</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>09/24 22:38:21</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>6410</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>SH6669</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>286885</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>35175.63</t>
+          <t>436885</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>11467</t>
+          <t>53247.92</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>11467</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>23708.63</t>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>41780.92</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5585070216/fb959c2cacc9c000a1cd5487b775e89da035f9898b2fed9930724428cc85cf6d/bill-all.xlsx
+++ b/bills/huixinjiqiren/-5585070216/fb959c2cacc9c000a1cd5487b775e89da035f9898b2fed9930724428cc85cf6d/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/30 22:50:49</t>
+          <t>10/04 11:10:41</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>18072.29</t>
+          <t>27380.95</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SH9982</t>
+          <t>SH6619</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/29 11:20:18</t>
+          <t>09/30 22:50:49</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>18072.29</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,7 +159,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/25 11:47:11</t>
+          <t>09/29 11:20:18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/24 21:20:03</t>
+          <t>09/25 11:47:11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>36885</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>4668.99</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,166 +243,181 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>09/24 21:20:03</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>36885</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>4668.99</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>SH9982</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>09/24 17:17:34</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>50000</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>7.8</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>6410.26</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/29 11:20:25</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>SH9982</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/24 22:41:05</t>
+          <t>09/29 11:20:25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>4669</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -412,7 +427,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>SH9982</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -424,83 +439,110 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>09/24 22:41:05</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>4669</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Nikotian01</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>09/24 22:38:21</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>6410</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>SH6669</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>436885</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>53247.92</t>
+          <t>666885</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>11467</t>
+          <t>80628.87</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>11467</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>41780.92</t>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>69161.87</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5585070216/fb959c2cacc9c000a1cd5487b775e89da035f9898b2fed9930724428cc85cf6d/bill-all.xlsx
+++ b/bills/huixinjiqiren/-5585070216/fb959c2cacc9c000a1cd5487b775e89da035f9898b2fed9930724428cc85cf6d/bill-all.xlsx
@@ -412,12 +412,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/29 11:20:25</t>
+          <t>10/04 11:10:52</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>588</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -427,7 +427,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>SH9982</t>
+          <t>SH6618</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -439,12 +439,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/24 22:41:05</t>
+          <t>09/29 11:20:25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>4669</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -454,7 +454,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>SH9982</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -466,83 +466,110 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>09/24 22:41:05</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>4669</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Nikotian01</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>09/24 22:38:21</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>6410</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>SH6669</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>666885</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>80628.87</t>
+          <t>666885</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>11467</t>
+          <t>80628.87</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>12055</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>69161.87</t>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>68573.87</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5585070216/fb959c2cacc9c000a1cd5487b775e89da035f9898b2fed9930724428cc85cf6d/bill-all.xlsx
+++ b/bills/huixinjiqiren/-5585070216/fb959c2cacc9c000a1cd5487b775e89da035f9898b2fed9930724428cc85cf6d/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/04 11:10:41</t>
+          <t>10/06 12:40:40</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>27380.95</t>
+          <t>9638.55</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SH6619</t>
+          <t>SH6662</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/30 22:50:49</t>
+          <t>10/04 11:10:41</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>18072.29</t>
+          <t>27380.95</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SH9982</t>
+          <t>SH6619</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/29 11:20:18</t>
+          <t>09/30 22:50:49</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>18072.29</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,7 +201,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/25 11:47:11</t>
+          <t>09/29 11:20:18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/24 21:20:03</t>
+          <t>09/25 11:47:11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>36885</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>4668.99</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,166 +285,181 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>09/24 21:20:03</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>36885</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>4668.99</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SH9982</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>09/24 17:17:34</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>50000</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>7.8</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>6410.26</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
+      <c r="F11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10/04 11:10:52</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>SH6618</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/29 11:20:25</t>
+          <t>10/04 11:10:52</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>588</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -454,7 +469,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SH9982</t>
+          <t>SH6618</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -466,12 +481,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/24 22:41:05</t>
+          <t>09/29 11:20:25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>4669</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -481,7 +496,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>SH9982</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -493,83 +508,110 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>09/24 22:41:05</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>4669</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Nikotian01</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>09/24 22:38:21</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>6410</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>SH6669</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>666885</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>80628.87</t>
+          <t>746885</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>12055</t>
+          <t>90267.43</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>12055</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>68573.87</t>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>78212.43</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5585070216/fb959c2cacc9c000a1cd5487b775e89da035f9898b2fed9930724428cc85cf6d/bill-all.xlsx
+++ b/bills/huixinjiqiren/-5585070216/fb959c2cacc9c000a1cd5487b775e89da035f9898b2fed9930724428cc85cf6d/bill-all.xlsx
@@ -454,12 +454,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10/04 11:10:52</t>
+          <t>10/06 12:40:54</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -469,7 +469,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SH6618</t>
+          <t>SH6662</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -481,12 +481,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/29 11:20:25</t>
+          <t>10/04 11:10:52</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>588</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -496,7 +496,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SH9982</t>
+          <t>SH6618</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -508,12 +508,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/24 22:41:05</t>
+          <t>09/29 11:20:25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>4669</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -523,7 +523,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>SH9982</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -535,83 +535,110 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>09/24 22:41:05</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>4669</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Nikotian01</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>09/24 22:38:21</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>6410</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>SH6669</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>746885</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>90267.43</t>
+          <t>746885</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>12055</t>
+          <t>90267.43</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>12243</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>78212.43</t>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>78024.43</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5585070216/fb959c2cacc9c000a1cd5487b775e89da035f9898b2fed9930724428cc85cf6d/bill-all.xlsx
+++ b/bills/huixinjiqiren/-5585070216/fb959c2cacc9c000a1cd5487b775e89da035f9898b2fed9930724428cc85cf6d/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/06 12:40:40</t>
+          <t>10/18 16:50:02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>9638.55</t>
+          <t>10714.29</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/04 11:10:41</t>
+          <t>10/06 12:40:40</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>27380.95</t>
+          <t>9638.55</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SH6619</t>
+          <t>SH6662</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/30 22:50:49</t>
+          <t>10/04 11:10:41</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>18072.29</t>
+          <t>27380.95</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SH9982</t>
+          <t>SH6619</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/29 11:20:18</t>
+          <t>09/30 22:50:49</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>18072.29</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,7 +243,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/25 11:47:11</t>
+          <t>09/29 11:20:18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/24 21:20:03</t>
+          <t>09/25 11:47:11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>36885</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4668.99</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,166 +327,181 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>09/24 21:20:03</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>36885</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>4668.99</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>SH9982</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>09/24 17:17:34</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>50000</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>7.8</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>6410.26</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="F12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10/06 12:40:54</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SH6662</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10/04 11:10:52</t>
+          <t>10/06 12:40:54</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -496,7 +511,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SH6618</t>
+          <t>SH6662</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -508,12 +523,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/29 11:20:25</t>
+          <t>10/04 11:10:52</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>588</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -523,7 +538,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SH9982</t>
+          <t>SH6618</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -535,12 +550,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/24 22:41:05</t>
+          <t>09/29 11:20:25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4669</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -550,7 +565,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>SH9982</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -562,83 +577,110 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>09/24 22:41:05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>4669</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Nikotian01</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>09/24 22:38:21</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>6410</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>SH6669</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>746885</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>90267.43</t>
+          <t>836885</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>12243</t>
+          <t>100981.71</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>12243</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>78024.43</t>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>88738.71</t>
         </is>
       </c>
     </row>
